--- a/SW1.1234/8I5RAGGN2U40Q0/Books/dist/P01/translation.xlsx
+++ b/SW1.1234/8I5RAGGN2U40Q0/Books/dist/P01/translation.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="52">
   <si>
     <t>Page No</t>
   </si>
@@ -48,16 +48,16 @@
     <t>meta</t>
   </si>
   <si>
+    <t>Compound Words</t>
+  </si>
+  <si>
     <t>blank.mp3</t>
   </si>
   <si>
     <t>title</t>
   </si>
   <si>
-    <t>Compound Words</t>
-  </si>
-  <si>
-    <t>Words Ending in -tion</t>
+    <t>P01_1.mp3</t>
   </si>
   <si>
     <t>Compound Words_Compound Words</t>
@@ -69,55 +69,79 @@
     <t>Word Power</t>
   </si>
   <si>
+    <t>P01_2.mp3</t>
+  </si>
+  <si>
     <t>Word Power_Word Power</t>
   </si>
   <si>
     <t>General Rule</t>
   </si>
   <si>
+    <t>P01_3.mp3</t>
+  </si>
+  <si>
     <t>General Rule_General Rule</t>
   </si>
   <si>
     <t>rainbow</t>
   </si>
   <si>
+    <t>rainbow.mp3</t>
+  </si>
+  <si>
     <t>rainbow_rainbow</t>
   </si>
   <si>
     <t>popcorn</t>
   </si>
   <si>
+    <t>popcorn.mp3</t>
+  </si>
+  <si>
     <t>popcorn_popcorn</t>
   </si>
   <si>
     <t>sidewalk</t>
   </si>
   <si>
+    <t>sidewalk.mp3</t>
+  </si>
+  <si>
     <t>sidewalk_sidewalk</t>
   </si>
   <si>
     <t>baseball</t>
   </si>
   <si>
+    <t>baseball.mp3</t>
+  </si>
+  <si>
     <t>baseball_baseball</t>
   </si>
   <si>
     <t>sunshine</t>
   </si>
   <si>
+    <t>sunshine.mp3</t>
+  </si>
+  <si>
     <t>sunshine_sunshine</t>
   </si>
   <si>
     <t>outside</t>
   </si>
   <si>
+    <t>outside.mp3</t>
+  </si>
+  <si>
     <t>outside_sunshine</t>
   </si>
   <si>
     <t>game-comprehension</t>
   </si>
   <si>
-    <t>rainbow_rainbow,rain bow_rain bow,rainbo_rainbo,rainbuw_rainbuw</t>
+    <t>rainbow_rainbow,rain bow_rain bow,rainboe_rainboe,ranbow_ranbow</t>
   </si>
   <si>
     <t>pop corn_pop corn,popcurn_popcurn,popcorn_popcorn,pupcon_pupcon</t>
@@ -138,7 +162,7 @@
     <t>Record the word!</t>
   </si>
   <si>
-    <t>What is question for write ups?</t>
+    <t>Listen and write what you hear.</t>
   </si>
   <si>
     <t>credits</t>
@@ -149,10 +173,10 @@
   <si>
     <t>&lt;sw-blurb&gt;
  &lt;sw-headline lang="EN"&gt;
-  Words Ending in -tion
+  Compound Words
  &lt;/sw-headline&gt;
  &lt;sw-headline lang="ES"&gt;
-  Words Ending in -tion
+  Compound Words
  &lt;/sw-headline&gt;
  &lt;table&gt;
   &lt;tr&gt;
@@ -217,7 +241,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="12.0"/>
       <color theme="1"/>
@@ -246,6 +270,10 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <color theme="1"/>
+      <name val="Arial"/>
+    </font>
+    <font>
       <sz val="10.0"/>
       <color theme="1"/>
       <name val="Arial"/>
@@ -253,7 +281,7 @@
     <font>
       <sz val="12.0"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="2">
@@ -292,7 +320,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="15">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -307,17 +335,28 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" wrapText="1"/>
+    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -580,10 +619,12 @@
       <c r="B2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="4"/>
+      <c r="C2" s="4" t="s">
+        <v>10</v>
+      </c>
       <c r="D2" s="4"/>
       <c r="E2" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F2" s="4"/>
       <c r="G2" s="4"/>
@@ -594,21 +635,21 @@
         <v>1.0</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D3" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="G3" s="6" t="s">
         <v>14</v>
       </c>
       <c r="H3" s="4"/>
@@ -626,14 +667,14 @@
       <c r="D4" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="4" t="s">
-        <v>10</v>
+      <c r="E4" s="5" t="s">
+        <v>17</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" ht="15.75" customHeight="1">
@@ -644,19 +685,19 @@
         <v>15</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>10</v>
+        <v>19</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>20</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6" ht="15.75" customHeight="1">
@@ -667,19 +708,19 @@
         <v>15</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>10</v>
+        <v>22</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>23</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1">
@@ -690,19 +731,19 @@
         <v>15</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>10</v>
+        <v>25</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>26</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1">
@@ -713,19 +754,19 @@
         <v>15</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>10</v>
+        <v>28</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9" ht="15.75" customHeight="1">
@@ -736,19 +777,19 @@
         <v>15</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>10</v>
+        <v>31</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>32</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1">
@@ -759,19 +800,19 @@
         <v>15</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>10</v>
+        <v>34</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>35</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" ht="15.75" customHeight="1">
@@ -782,331 +823,331 @@
         <v>15</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>10</v>
+        <v>37</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>38</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
     </row>
     <row r="12" ht="15.75" customHeight="1">
       <c r="A12" s="3">
         <v>10.0</v>
       </c>
-      <c r="B12" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="F12" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="G12" s="9"/>
+      <c r="B12" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="G12" s="10"/>
       <c r="H12" s="4" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13" ht="15.75" customHeight="1">
       <c r="A13" s="3">
         <v>11.0</v>
       </c>
-      <c r="B13" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="F13" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="G13" s="9"/>
+      <c r="B13" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="F13" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="G13" s="10"/>
       <c r="H13" s="4" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
     </row>
     <row r="14" ht="15.75" customHeight="1">
       <c r="A14" s="3">
         <v>12.0</v>
       </c>
-      <c r="B14" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="F14" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="G14" s="9"/>
+      <c r="B14" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="F14" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="G14" s="10"/>
       <c r="H14" s="4" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1">
       <c r="A15" s="4">
         <v>13.0</v>
       </c>
-      <c r="B15" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="F15" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="G15" s="9"/>
+      <c r="B15" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="F15" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="G15" s="10"/>
       <c r="H15" s="4" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16" ht="15.75" customHeight="1">
       <c r="A16" s="4">
         <v>14.0</v>
       </c>
-      <c r="B16" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="F16" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="G16" s="9"/>
+      <c r="B16" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="F16" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="G16" s="10"/>
       <c r="H16" s="4" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17" ht="15.75" customHeight="1">
-      <c r="A17" s="7">
+      <c r="A17" s="8">
         <v>15.0</v>
       </c>
-      <c r="B17" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="F17" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="G17" s="9"/>
+      <c r="B17" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="F17" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="G17" s="10"/>
       <c r="H17" s="4" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
     </row>
     <row r="18" ht="15.75" customHeight="1">
       <c r="A18" s="4">
         <v>16.0</v>
       </c>
-      <c r="B18" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>39</v>
+      <c r="B18" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>47</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="19" ht="15.75" customHeight="1">
       <c r="A19" s="4">
         <v>17.0</v>
       </c>
-      <c r="B19" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="C19" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>39</v>
+      <c r="B19" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>47</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="20" ht="15.75" customHeight="1">
       <c r="A20" s="4">
         <v>18.0</v>
       </c>
-      <c r="B20" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="C20" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="D20" s="7" t="s">
-        <v>39</v>
+      <c r="B20" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>47</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="4">
         <v>19.0</v>
       </c>
-      <c r="B21" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="C21" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="D21" s="7" t="s">
-        <v>39</v>
+      <c r="B21" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="D21" s="8" t="s">
+        <v>47</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="4">
         <v>20.0</v>
       </c>
-      <c r="B22" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="C22" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="D22" s="7" t="s">
-        <v>39</v>
+      <c r="B22" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="D22" s="8" t="s">
+        <v>47</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="4">
         <v>21.0</v>
       </c>
-      <c r="B23" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="C23" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="D23" s="7" t="s">
-        <v>39</v>
+      <c r="B23" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>47</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="4">
         <v>22.0</v>
       </c>
-      <c r="B24" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="C24" s="10" t="s">
+      <c r="B24" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="D24" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="E24" s="4" t="s">
-        <v>10</v>
+      <c r="C24" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="D24" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="E24" s="13" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="4">
         <v>23.0</v>
       </c>
-      <c r="B25" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="C25" s="10" t="s">
+      <c r="B25" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="D25" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="E25" s="4" t="s">
-        <v>10</v>
+      <c r="C25" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="D25" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="E25" s="13" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="4">
         <v>24.0</v>
       </c>
-      <c r="B26" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="C26" s="10" t="s">
+      <c r="B26" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="D26" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="E26" s="4" t="s">
-        <v>10</v>
+      <c r="C26" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="D26" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="E26" s="13" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="4">
         <v>25.0</v>
       </c>
-      <c r="B27" s="7" t="s">
+      <c r="B27" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="C27" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="D27" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="E27" s="13" t="s">
         <v>32</v>
-      </c>
-      <c r="C27" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="D27" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="E27" s="4" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="4">
         <v>26.0</v>
       </c>
-      <c r="B28" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="C28" s="10" t="s">
+      <c r="B28" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="D28" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="E28" s="4" t="s">
-        <v>10</v>
+      <c r="C28" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="D28" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="4">
         <v>27.0</v>
       </c>
-      <c r="B29" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="C29" s="10" t="s">
+      <c r="B29" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="D29" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="E29" s="4" t="s">
-        <v>10</v>
+      <c r="C29" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="D29" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="7">
+      <c r="A30" s="8">
         <v>28.0</v>
       </c>
-      <c r="B30" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="C30" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="I30" s="11" t="s">
-        <v>43</v>
+      <c r="B30" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="C30" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="I30" s="14" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="6"/>
+      <c r="A31" s="7"/>
     </row>
     <row r="32" ht="15.75" customHeight="1"/>
     <row r="33" ht="15.75" customHeight="1"/>
